--- a/Calculator.xlsx
+++ b/Calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Denis\source\repos\ThermodynamicsSolarHeatingAddon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5A5EF-F385-4C93-AEC9-29DF6DBCA436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B422C1-5AAF-4B98-84F6-387E3809D3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{B68D1F94-C044-4242-9F23-6F7FF63C8FE2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{B68D1F94-C044-4242-9F23-6F7FF63C8FE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Material</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>EnergyFlow, w/m^2</t>
+  </si>
+  <si>
+    <t>Outer layer</t>
   </si>
 </sst>
 </file>
@@ -103,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -111,14 +114,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,27 +501,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA21B03E-B4DE-40CE-8EC0-BCCAC7D82E6D}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -465,20 +531,20 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.85</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="G2" t="s">
@@ -495,20 +561,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.15</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.05</v>
       </c>
       <c r="G3" t="s">
@@ -518,159 +584,169 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.3</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.15</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
+      <c r="C9" s="1">
         <f>4*COS($H$2)*($H$1*($B$2*B$2)+($H$1*$B$4*MIN($B$3,B$3/$H$3))+$H$1*($B$2*B$4*B$3))</f>
         <v>1250</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="1">
         <f>4*COS($H$2)*($H$1*($B$2*C$2)+($H$1*$B$4*MIN($B$3,C$3/$H$3))+$H$1*($B$2*C$4*C$3))</f>
         <v>1000.0000000000001</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="1">
         <f>4*COS($H$2)*($H$1*($B$2*D$2)+($H$1*$B$4*MIN($B$3,D$3/$H$3))+$H$1*($B$2*D$4*D$3))</f>
         <v>187.5</v>
       </c>
-      <c r="E9">
+      <c r="F9" s="1">
         <f>4*COS($H$2)*($H$1*($B$2*E$2)+($H$1*$B$4*MIN($B$3,E$3/$H$3))+$H$1*($B$2*E$4*E$3))</f>
         <v>62.500000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10">
+      <c r="C10" s="1">
         <f>4*COS($H$2)*($H$1*($C$2*B$2)+($H$1*$C$4*MIN($C$3,B$3/$H$3))+$H$1*($C$2*B$4*B$3))</f>
         <v>600</v>
       </c>
-      <c r="C10">
+      <c r="D10" s="1">
         <f>4*COS($H$2)*($H$1*($C$2*C$2)+($H$1*$C$4*MIN($C$3,C$3/$H$3))+$H$1*($C$2*C$4*C$3))</f>
         <v>500.00000000000006</v>
       </c>
-      <c r="D10">
+      <c r="E10" s="1">
         <f>4*COS($H$2)*($H$1*($C$2*D$2)+($H$1*$C$4*MIN($C$3,D$3/$H$3))+$H$1*($C$2*D$4*D$3))</f>
         <v>93.75</v>
       </c>
-      <c r="E10">
+      <c r="F10" s="1">
         <f>4*COS($H$2)*($H$1*($C$2*E$2)+($H$1*$C$4*MIN($C$3,E$3/$H$3))+$H$1*($C$2*E$4*E$3))</f>
         <v>31.250000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B11">
+      <c r="C11" s="1">
         <f>4*COS($H$2)*($H$1*($D$2*B$2)+($H$1*$D$4*MIN($D$3,B$3/$H$3))+$H$1*($D$2*B$4*B$3))</f>
         <v>1350</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="1">
         <f>4*COS($H$2)*($H$1*($D$2*C$2)+($H$1*$D$4*MIN($D$3,C$3/$H$3))+$H$1*($D$2*C$4*C$3))</f>
         <v>585</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="1">
         <f>4*COS($H$2)*($H$1*($D$2*D$2)+($H$1*$D$4*MIN($D$3,D$3/$H$3))+$H$1*($D$2*D$4*D$3))</f>
         <v>3738.7499999999995</v>
       </c>
-      <c r="E11">
+      <c r="F11" s="1">
         <f>4*COS($H$2)*($H$1*($D$2*E$2)+($H$1*$D$4*MIN($D$3,E$3/$H$3))+$H$1*($D$2*E$4*E$3))</f>
         <v>127.08333333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12">
+      <c r="C12" s="1">
         <f>4*COS($H$2)*($H$1*($E$2*B$2)+($H$1*$E$4*MIN($E$3,B$3/$H$3))+$H$1*($E$2*B$4*B$3))</f>
         <v>125</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="1">
         <f>4*COS($H$2)*($H$1*($E$2*C$2)+($H$1*$E$4*MIN($E$3,C$3/$H$3))+$H$1*($E$2*C$4*C$3))</f>
         <v>125</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="1">
         <f>4*COS($H$2)*($H$1*($E$2*D$2)+($H$1*$E$4*MIN($E$3,D$3/$H$3))+$H$1*($E$2*D$4*D$3))</f>
         <v>125</v>
       </c>
-      <c r="E12">
+      <c r="F12" s="1">
         <f>4*COS($H$2)*($H$1*($E$2*E$2)+($H$1*$E$4*MIN($E$3,E$3/$H$3))+$H$1*($E$2*E$4*E$3))</f>
         <v>104.16666666666667</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13">
+      <c r="C13" s="1">
         <f>4*COS($H$2)*($H$1*(B$2)+($H$1*B4*B$3))</f>
         <v>1500</v>
       </c>
-      <c r="C13">
+      <c r="D13" s="1">
         <f>4*COS($H$2)*($H$1*(C$2)+($H$1*C4*C$3))</f>
         <v>600</v>
       </c>
-      <c r="D13">
-        <f t="shared" ref="D13:E13" si="0">4*COS($H$2)*($H$1*(D$2)+($H$1*D4*D$3))</f>
+      <c r="E13" s="1">
+        <f>4*COS($H$2)*($H$1*(D$2)+($H$1*D4*D$3))</f>
         <v>4325</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
+      <c r="F13" s="1">
+        <f>4*COS($H$2)*($H$1*(E$2)+($H$1*E4*E$3))</f>
         <v>125</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B7:E7"/>
+  <mergeCells count="2">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A8:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
